--- a/grupos/3ARHV - Estadisticos 20221.xlsx
+++ b/grupos/3ARHV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -179,18 +179,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
@@ -206,6 +206,69 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>ZETINA</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>XOCHITL JOSELINE</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>ANIELKA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
     <t>ANDRADE</t>
   </si>
   <si>
@@ -215,51 +278,30 @@
     <t>CASTRO</t>
   </si>
   <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
     <t>CIRUELO</t>
   </si>
   <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>HERRERA</t>
   </si>
   <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MAYAHUA</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>OREA</t>
-  </si>
-  <si>
     <t>ORTIZ</t>
   </si>
   <si>
@@ -272,9 +314,6 @@
     <t>ROMERO</t>
   </si>
   <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
     <t>ROMANOS</t>
   </si>
   <si>
@@ -284,33 +323,18 @@
     <t>TETLA</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
     <t>VEGA</t>
   </si>
   <si>
-    <t>ZETINA</t>
-  </si>
-  <si>
     <t>ARIAS</t>
   </si>
   <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
     <t>TORRES</t>
   </si>
   <si>
@@ -359,9 +383,6 @@
     <t>ROJAS</t>
   </si>
   <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
     <t>MARISOL</t>
   </si>
   <si>
@@ -371,18 +392,9 @@
     <t>ELIZABETH</t>
   </si>
   <si>
-    <t>XOCHITL JOSELINE</t>
-  </si>
-  <si>
     <t>GABRIELA ELIZABETH</t>
   </si>
   <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
     <t>ZAYRA</t>
   </si>
   <si>
@@ -416,9 +428,6 @@
     <t>VALERIA</t>
   </si>
   <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
     <t>ANGEL GABRIEL</t>
   </si>
   <si>
@@ -431,9 +440,6 @@
     <t>INGRID CRISTEL</t>
   </si>
   <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
     <t>DANIELA</t>
   </si>
   <si>
@@ -446,16 +452,10 @@
     <t>YAZURI</t>
   </si>
   <si>
-    <t>ANIELKA</t>
-  </si>
-  <si>
     <t>XIMENA</t>
   </si>
   <si>
     <t>HANIA ZARETH</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
   </si>
 </sst>
 </file>
@@ -950,7 +950,7 @@
         <v>7</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>9</v>
@@ -1004,7 +1004,7 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1027,7 +1027,7 @@
         <v>8</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F5">
         <v>8</v>
@@ -1081,7 +1081,7 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -1104,7 +1104,7 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -1158,7 +1158,7 @@
         <v>10</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1181,7 +1181,7 @@
         <v>-1</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -1235,7 +1235,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1258,7 +1258,7 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F8">
         <v>8</v>
@@ -1312,7 +1312,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1335,7 +1335,7 @@
         <v>-1</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -1389,7 +1389,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -1412,7 +1412,7 @@
         <v>-1</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F10">
         <v>7</v>
@@ -1466,7 +1466,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1489,7 +1489,7 @@
         <v>9</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -1543,7 +1543,7 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1566,7 +1566,7 @@
         <v>8</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F12">
         <v>10</v>
@@ -1620,7 +1620,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1643,7 +1643,7 @@
         <v>9</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F13">
         <v>8</v>
@@ -1697,7 +1697,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>8</v>
@@ -1720,7 +1720,7 @@
         <v>8</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F14">
         <v>9</v>
@@ -1774,7 +1774,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X14">
         <v>9</v>
@@ -1797,7 +1797,7 @@
         <v>10</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F15">
         <v>9</v>
@@ -1851,7 +1851,7 @@
         <v>10</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -1874,7 +1874,7 @@
         <v>8</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F16">
         <v>10</v>
@@ -1928,7 +1928,7 @@
         <v>8</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -1951,7 +1951,7 @@
         <v>7</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F17">
         <v>8</v>
@@ -2005,7 +2005,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2028,7 +2028,7 @@
         <v>10</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F18">
         <v>10</v>
@@ -2082,7 +2082,7 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -2105,7 +2105,7 @@
         <v>7</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F19">
         <v>8</v>
@@ -2159,7 +2159,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -2182,7 +2182,7 @@
         <v>9</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F20">
         <v>10</v>
@@ -2236,7 +2236,7 @@
         <v>9</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -2259,7 +2259,7 @@
         <v>9</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F21">
         <v>8</v>
@@ -2313,7 +2313,7 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2413,7 +2413,7 @@
         <v>9</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F23">
         <v>9</v>
@@ -2467,7 +2467,7 @@
         <v>9</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>9</v>
@@ -2490,7 +2490,7 @@
         <v>8</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F24">
         <v>10</v>
@@ -2544,7 +2544,7 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2567,7 +2567,7 @@
         <v>9</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F25">
         <v>10</v>
@@ -2621,7 +2621,7 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2644,7 +2644,7 @@
         <v>-1</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F26">
         <v>6</v>
@@ -2698,7 +2698,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>6</v>
@@ -2721,7 +2721,7 @@
         <v>7</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F27">
         <v>9</v>
@@ -2775,7 +2775,7 @@
         <v>7</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -2798,7 +2798,7 @@
         <v>6</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F28">
         <v>8</v>
@@ -2852,7 +2852,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -2875,7 +2875,7 @@
         <v>9</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F29">
         <v>10</v>
@@ -2929,7 +2929,7 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -2952,7 +2952,7 @@
         <v>7</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F30">
         <v>8</v>
@@ -3006,7 +3006,7 @@
         <v>7</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>8</v>
@@ -3029,7 +3029,7 @@
         <v>6</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F31">
         <v>8</v>
@@ -3083,7 +3083,7 @@
         <v>6</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -3183,7 +3183,7 @@
         <v>8</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F33">
         <v>10</v>
@@ -3237,7 +3237,7 @@
         <v>8</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3260,7 +3260,7 @@
         <v>7</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F34">
         <v>10</v>
@@ -3314,7 +3314,7 @@
         <v>7</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -3337,7 +3337,7 @@
         <v>-1</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F35">
         <v>5</v>
@@ -3391,7 +3391,7 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>5</v>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -3462,27 +3462,30 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>78.13</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>8.1</v>
+      </c>
       <c r="I2">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -3494,27 +3497,27 @@
         <v>25</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F3">
         <v>78.13</v>
       </c>
       <c r="G3">
+        <v>21.88</v>
+      </c>
+      <c r="H3">
+        <v>7.7</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="H3">
-        <v>8.1</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
-      </c>
       <c r="J3">
-        <v>21.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3523,19 +3526,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>78.13</v>
+        <v>81.25</v>
       </c>
       <c r="G4">
-        <v>21.88</v>
+        <v>18.75</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3546,7 +3549,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -3555,25 +3558,25 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>81.25</v>
+        <v>90.63</v>
       </c>
       <c r="G5">
-        <v>18.75</v>
+        <v>3.13</v>
       </c>
       <c r="H5">
         <v>8.199999999999999</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3581,7 +3584,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6">
         <v>32</v>
@@ -3647,7 +3650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3676,19 +3679,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920029</v>
+        <v>20330051920117</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>53</v>
@@ -3696,19 +3699,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920031</v>
+        <v>21330051920036</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>53</v>
@@ -3716,19 +3719,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920034</v>
+        <v>21330051920037</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>53</v>
@@ -3736,47 +3739,47 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920117</v>
+        <v>21330051920053</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920117</v>
+        <v>21330051920053</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920035</v>
+        <v>21330051920058</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
@@ -3785,10 +3788,10 @@
         <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>53</v>
@@ -3796,661 +3799,61 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920036</v>
+        <v>21330051920064</v>
       </c>
       <c r="B8" t="s">
         <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920036</v>
+        <v>21330051920064</v>
       </c>
       <c r="B9" t="s">
         <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920037</v>
+        <v>21330051920070</v>
       </c>
       <c r="B10" t="s">
         <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920037</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" t="s">
-        <v>120</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920038</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920390</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>98</v>
-      </c>
-      <c r="D13" t="s">
-        <v>122</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920040</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" t="s">
-        <v>123</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920041</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" t="s">
-        <v>124</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920043</v>
-      </c>
-      <c r="B16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" t="s">
-        <v>125</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920045</v>
-      </c>
-      <c r="B17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" t="s">
-        <v>101</v>
-      </c>
-      <c r="D17" t="s">
-        <v>126</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920046</v>
-      </c>
-      <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" t="s">
-        <v>127</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920047</v>
-      </c>
-      <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" t="s">
-        <v>128</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920048</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20" t="s">
-        <v>129</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920050</v>
-      </c>
-      <c r="B21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" t="s">
-        <v>104</v>
-      </c>
-      <c r="D21" t="s">
-        <v>130</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920051</v>
-      </c>
-      <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" t="s">
-        <v>131</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920053</v>
-      </c>
-      <c r="B23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" t="s">
-        <v>132</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920053</v>
-      </c>
-      <c r="B24" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" t="s">
-        <v>132</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920054</v>
-      </c>
-      <c r="B25" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" t="s">
-        <v>133</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920055</v>
-      </c>
-      <c r="B26" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" t="s">
-        <v>134</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920056</v>
-      </c>
-      <c r="B27" t="s">
-        <v>82</v>
-      </c>
-      <c r="C27" t="s">
-        <v>108</v>
-      </c>
-      <c r="D27" t="s">
-        <v>135</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920057</v>
-      </c>
-      <c r="B28" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" t="s">
-        <v>73</v>
-      </c>
-      <c r="D28" t="s">
-        <v>136</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920058</v>
-      </c>
-      <c r="B29" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" t="s">
-        <v>73</v>
-      </c>
-      <c r="D29" t="s">
-        <v>137</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920058</v>
-      </c>
-      <c r="B30" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" t="s">
-        <v>73</v>
-      </c>
-      <c r="D30" t="s">
-        <v>137</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920059</v>
-      </c>
-      <c r="B31" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" t="s">
-        <v>109</v>
-      </c>
-      <c r="D31" t="s">
-        <v>138</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920060</v>
-      </c>
-      <c r="B32" t="s">
-        <v>83</v>
-      </c>
-      <c r="C32" t="s">
-        <v>110</v>
-      </c>
-      <c r="D32" t="s">
-        <v>139</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920062</v>
-      </c>
-      <c r="B33" t="s">
-        <v>86</v>
-      </c>
-      <c r="C33" t="s">
-        <v>83</v>
-      </c>
-      <c r="D33" t="s">
-        <v>140</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920063</v>
-      </c>
-      <c r="B34" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" t="s">
-        <v>111</v>
-      </c>
-      <c r="D34" t="s">
-        <v>141</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920064</v>
-      </c>
-      <c r="B35" t="s">
-        <v>88</v>
-      </c>
-      <c r="C35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" t="s">
-        <v>142</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920064</v>
-      </c>
-      <c r="B36" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" t="s">
-        <v>142</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920065</v>
-      </c>
-      <c r="B37" t="s">
-        <v>89</v>
-      </c>
-      <c r="C37" t="s">
-        <v>101</v>
-      </c>
-      <c r="D37" t="s">
-        <v>143</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920067</v>
-      </c>
-      <c r="B38" t="s">
-        <v>90</v>
-      </c>
-      <c r="C38" t="s">
-        <v>112</v>
-      </c>
-      <c r="D38" t="s">
-        <v>144</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920070</v>
-      </c>
-      <c r="B39" t="s">
-        <v>91</v>
-      </c>
-      <c r="C39" t="s">
-        <v>113</v>
-      </c>
-      <c r="D39" t="s">
-        <v>145</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920070</v>
-      </c>
-      <c r="B40" t="s">
-        <v>91</v>
-      </c>
-      <c r="C40" t="s">
-        <v>113</v>
-      </c>
-      <c r="D40" t="s">
-        <v>145</v>
-      </c>
-      <c r="E40" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" t="s">
         <v>53</v>
       </c>
     </row>
@@ -4487,16 +3890,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920117</v>
+        <v>21330051920053</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -4504,16 +3907,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920036</v>
+        <v>21330051920064</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -4521,70 +3924,70 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920037</v>
+        <v>20330051920117</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920053</v>
+        <v>21330051920036</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920058</v>
+        <v>21330051920037</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920064</v>
+        <v>21330051920058</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4592,16 +3995,16 @@
         <v>21330051920070</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4609,16 +4012,16 @@
         <v>21330051920029</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
         <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4626,16 +4029,16 @@
         <v>21330051920031</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4643,16 +4046,16 @@
         <v>21330051920034</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4660,16 +4063,16 @@
         <v>21330051920035</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
         <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4677,16 +4080,16 @@
         <v>21330051920038</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -4694,16 +4097,16 @@
         <v>21330051920390</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4711,16 +4114,16 @@
         <v>21330051920040</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -4728,16 +4131,16 @@
         <v>21330051920041</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -4745,16 +4148,16 @@
         <v>21330051920043</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -4765,13 +4168,13 @@
         <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -4779,16 +4182,16 @@
         <v>21330051920046</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -4796,16 +4199,16 @@
         <v>21330051920047</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -4813,16 +4216,16 @@
         <v>21330051920048</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -4830,16 +4233,16 @@
         <v>21330051920050</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -4847,16 +4250,16 @@
         <v>21330051920051</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -4864,16 +4267,16 @@
         <v>21330051920054</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -4881,16 +4284,16 @@
         <v>21330051920055</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -4898,16 +4301,16 @@
         <v>21330051920056</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -4915,16 +4318,16 @@
         <v>21330051920057</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
         <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -4932,16 +4335,16 @@
         <v>21330051920059</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -4949,16 +4352,16 @@
         <v>21330051920060</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -4966,16 +4369,16 @@
         <v>21330051920062</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="D30" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -4983,16 +4386,16 @@
         <v>21330051920063</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -5000,16 +4403,16 @@
         <v>21330051920065</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -5017,16 +4420,16 @@
         <v>21330051920067</v>
       </c>
       <c r="B33" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5036,7 +4439,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5068,65 +4471,65 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920046</v>
+        <v>21330051920036</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920046</v>
+        <v>21330051920036</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920029</v>
+        <v>21330051920037</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>53</v>
@@ -5137,531 +4540,71 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920031</v>
+        <v>21330051920037</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920034</v>
+        <v>21330051920041</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920035</v>
+        <v>21330051920046</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920038</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" t="s">
-        <v>121</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920390</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D9" t="s">
-        <v>122</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920040</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920041</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D11" t="s">
-        <v>124</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920043</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D12" t="s">
-        <v>125</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920045</v>
-      </c>
-      <c r="B13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" t="s">
-        <v>101</v>
-      </c>
-      <c r="D13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920047</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" t="s">
-        <v>128</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920048</v>
-      </c>
-      <c r="B15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D15" t="s">
-        <v>129</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920050</v>
-      </c>
-      <c r="B16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" t="s">
-        <v>130</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920051</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" t="s">
-        <v>105</v>
-      </c>
-      <c r="D17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920054</v>
-      </c>
-      <c r="B18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" t="s">
-        <v>106</v>
-      </c>
-      <c r="D18" t="s">
-        <v>133</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920055</v>
-      </c>
-      <c r="B19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" t="s">
-        <v>134</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920056</v>
-      </c>
-      <c r="B20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" t="s">
-        <v>135</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920057</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21" t="s">
-        <v>136</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920059</v>
-      </c>
-      <c r="B22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" t="s">
-        <v>138</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920060</v>
-      </c>
-      <c r="B23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" t="s">
-        <v>110</v>
-      </c>
-      <c r="D23" t="s">
-        <v>139</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920062</v>
-      </c>
-      <c r="B24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" t="s">
-        <v>140</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920063</v>
-      </c>
-      <c r="B25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" t="s">
-        <v>111</v>
-      </c>
-      <c r="D25" t="s">
-        <v>141</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>53</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920065</v>
-      </c>
-      <c r="B26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" t="s">
-        <v>101</v>
-      </c>
-      <c r="D26" t="s">
-        <v>143</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>53</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920067</v>
-      </c>
-      <c r="B27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" t="s">
-        <v>112</v>
-      </c>
-      <c r="D27" t="s">
-        <v>144</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/3ARHV - Estadisticos 20221.xlsx
+++ b/grupos/3ARHV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -68,7 +68,7 @@
     <t>CHAVEZ TEPOLE XOCHITL JOSELINE</t>
   </si>
   <si>
-    <t>CIRUELO HERNANDEZ GABRIELA ELIZABETH</t>
+    <t>CIRUELO HERNANDEZ GABRIELA ELIZABET</t>
   </si>
   <si>
     <t>COMIHUA SANCHEZ ALEJANDRO GABRIEL</t>
@@ -137,7 +137,7 @@
     <t>TETLA TEXCAHUA YAZURI</t>
   </si>
   <si>
-    <t>TLAXCALTECALT ROMERO KARLA JAZMIN</t>
+    <t>TLAXCALTECATL ROMERO KARLA JAZMIN</t>
   </si>
   <si>
     <t>TRUJILLO FLORES ANIELKA</t>
@@ -185,15 +185,15 @@
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Mendoza Velazquez Laura Elena</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -206,27 +206,108 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ANIELKA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
     <t>CHAVEZ</t>
   </si>
   <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
     <t>COMIHUA</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>OREA</t>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
   </si>
   <si>
     <t>ROMAN</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>TLAXCALTECATL</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>VEGA</t>
   </si>
   <si>
     <t>ZETINA</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
     <t>TEPOLE</t>
   </si>
   <si>
@@ -236,226 +317,145 @@
     <t>DEL ROSARIO</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>LEPE</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>VALLEJO</t>
   </si>
   <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
     <t>XOCHITL JOSELINE</t>
   </si>
   <si>
+    <t>GABRIELA ELIZABET</t>
+  </si>
+  <si>
     <t>ALEJANDRO GABRIEL</t>
   </si>
   <si>
     <t>CARLA ESTEFANIA</t>
   </si>
   <si>
-    <t>JOSE MANUEL</t>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>ZENON AXXEL</t>
+  </si>
+  <si>
+    <t>GIOVANI</t>
+  </si>
+  <si>
+    <t>EMMANUEL DAVID</t>
+  </si>
+  <si>
+    <t>ZURY BETZABE</t>
+  </si>
+  <si>
+    <t>MIA ARANZA</t>
+  </si>
+  <si>
+    <t>NUBIA NAHOMI</t>
+  </si>
+  <si>
+    <t>MICHEL</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>ANDREA YONETH</t>
+  </si>
+  <si>
+    <t>INGRID CRISTEL</t>
   </si>
   <si>
     <t>MARIANA</t>
   </si>
   <si>
-    <t>ANIELKA</t>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>SARAHI</t>
+  </si>
+  <si>
+    <t>KARLA JAZMIN</t>
+  </si>
+  <si>
+    <t>YAZURI</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>LEPE</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABETH</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
-    <t>ZENON AXXEL</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
-  </si>
-  <si>
-    <t>EMMANUEL DAVID</t>
-  </si>
-  <si>
-    <t>ZURY BETZABE</t>
-  </si>
-  <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>NUBIA NAHOMI</t>
-  </si>
-  <si>
-    <t>MICHEL</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>ANDREA YONETH</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
-  </si>
-  <si>
-    <t>KARLA JAZMIN</t>
-  </si>
-  <si>
-    <t>YAZURI</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
   </si>
 </sst>
 </file>
@@ -959,19 +959,19 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -995,13 +995,13 @@
         <v>-1</v>
       </c>
       <c r="T4">
+        <v>8</v>
+      </c>
+      <c r="U4">
+        <v>9</v>
+      </c>
+      <c r="V4">
         <v>6</v>
-      </c>
-      <c r="U4">
-        <v>9</v>
-      </c>
-      <c r="V4">
-        <v>7</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -1036,19 +1036,19 @@
         <v>7</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1072,19 +1072,19 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5">
         <v>9</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>8</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -1113,19 +1113,19 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1178,7 +1178,7 @@
         <v>8</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>7</v>
@@ -1190,19 +1190,19 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1226,19 +1226,19 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>7</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1267,19 +1267,19 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1303,19 +1303,19 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>10</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>8</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1332,7 +1332,7 @@
         <v>8</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E9">
         <v>6</v>
@@ -1344,19 +1344,19 @@
         <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1386,7 +1386,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>6</v>
@@ -1409,7 +1409,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -1421,19 +1421,19 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1463,7 +1463,7 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>6</v>
@@ -1498,19 +1498,19 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1540,7 +1540,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1575,19 +1575,19 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1617,7 +1617,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1652,19 +1652,19 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1700,7 +1700,7 @@
         <v>9</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>8</v>
@@ -1729,19 +1729,19 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1765,13 +1765,13 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>10</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>5</v>
@@ -1806,19 +1806,19 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1854,7 +1854,7 @@
         <v>10</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1883,19 +1883,19 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1925,7 +1925,7 @@
         <v>8</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -1960,19 +1960,19 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -1996,7 +1996,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>10</v>
@@ -2037,19 +2037,19 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2114,19 +2114,19 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2191,19 +2191,19 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2227,13 +2227,13 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>10</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -2268,19 +2268,19 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2304,19 +2304,19 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>10</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W21">
         <v>9</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2333,7 +2333,7 @@
         <v>5</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>-1</v>
@@ -2345,19 +2345,19 @@
         <v>5</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I22">
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2381,13 +2381,13 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U22">
         <v>5</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>-1</v>
@@ -2422,19 +2422,19 @@
         <v>9</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2499,19 +2499,19 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2535,13 +2535,13 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>10</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2576,19 +2576,19 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2612,13 +2612,13 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U25">
         <v>10</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2641,7 +2641,7 @@
         <v>8</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E26">
         <v>8</v>
@@ -2653,19 +2653,19 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I26">
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2689,19 +2689,19 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U26">
         <v>8</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W26">
         <v>8</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -2730,19 +2730,19 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2772,13 +2772,13 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>9</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2807,19 +2807,19 @@
         <v>7</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2843,19 +2843,19 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U28">
         <v>10</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>8</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -2884,19 +2884,19 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -2961,19 +2961,19 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I30">
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -2997,13 +2997,13 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>9</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3038,19 +3038,19 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I31">
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3074,13 +3074,13 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>8</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W31">
         <v>8</v>
@@ -3103,7 +3103,7 @@
         <v>5</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E32">
         <v>-1</v>
@@ -3115,19 +3115,19 @@
         <v>5</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I32">
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3157,7 +3157,7 @@
         <v>5</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W32">
         <v>-1</v>
@@ -3192,19 +3192,19 @@
         <v>9</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3234,13 +3234,13 @@
         <v>9</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>10</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y33">
         <v>9</v>
@@ -3269,19 +3269,19 @@
         <v>7</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I34">
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3334,7 +3334,7 @@
         <v>5</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E35">
         <v>6</v>
@@ -3346,19 +3346,19 @@
         <v>5</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I35">
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3382,13 +3382,13 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U35">
         <v>5</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W35">
         <v>6</v>
@@ -3465,22 +3465,22 @@
         <v>25</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
         <v>78.13</v>
       </c>
       <c r="G2">
+        <v>21.88</v>
+      </c>
+      <c r="H2">
+        <v>7.9</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="H2">
-        <v>8.1</v>
-      </c>
-      <c r="I2">
-        <v>7</v>
-      </c>
       <c r="J2">
-        <v>21.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3517,7 +3517,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
@@ -3526,19 +3526,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>81.25</v>
+        <v>84.38</v>
       </c>
       <c r="G4">
-        <v>18.75</v>
+        <v>15.63</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3613,7 +3613,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
@@ -3622,19 +3622,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>90.63</v>
+        <v>96.88</v>
       </c>
       <c r="G7">
-        <v>9.380000000000001</v>
+        <v>3.13</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3650,7 +3650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3679,182 +3679,42 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920117</v>
+        <v>21330051920053</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920036</v>
+        <v>21330051920064</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920037</v>
-      </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920053</v>
-      </c>
-      <c r="B5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920053</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920058</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920064</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920064</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920070</v>
-      </c>
-      <c r="B10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -3893,16 +3753,16 @@
         <v>21330051920053</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3910,112 +3770,112 @@
         <v>21330051920064</v>
       </c>
       <c r="B3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" t="s">
         <v>67</v>
       </c>
-      <c r="C3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" t="s">
-        <v>81</v>
-      </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920117</v>
+        <v>21330051920029</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920036</v>
+        <v>21330051920031</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920037</v>
+        <v>21330051920034</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920058</v>
+        <v>20330051920117</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920070</v>
+        <v>21330051920035</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920029</v>
+        <v>21330051920036</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
         <v>121</v>
@@ -4026,13 +3886,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920031</v>
+        <v>21330051920037</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
         <v>122</v>
@@ -4043,13 +3903,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920034</v>
+        <v>21330051920038</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D11" t="s">
         <v>123</v>
@@ -4060,13 +3920,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920035</v>
+        <v>21330051920390</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
         <v>124</v>
@@ -4077,13 +3937,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920038</v>
+        <v>21330051920040</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
         <v>125</v>
@@ -4094,13 +3954,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920390</v>
+        <v>21330051920041</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
         <v>126</v>
@@ -4111,13 +3971,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920040</v>
+        <v>21330051920043</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
         <v>127</v>
@@ -4128,13 +3988,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920041</v>
+        <v>21330051920045</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
         <v>128</v>
@@ -4145,13 +4005,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920043</v>
+        <v>21330051920046</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
         <v>129</v>
@@ -4162,13 +4022,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920045</v>
+        <v>21330051920047</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
         <v>130</v>
@@ -4179,13 +4039,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920046</v>
+        <v>21330051920048</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
         <v>131</v>
@@ -4196,13 +4056,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920047</v>
+        <v>21330051920050</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
         <v>132</v>
@@ -4213,13 +4073,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920048</v>
+        <v>21330051920051</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
@@ -4230,13 +4090,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920050</v>
+        <v>21330051920054</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
         <v>134</v>
@@ -4247,13 +4107,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920051</v>
+        <v>21330051920055</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
         <v>135</v>
@@ -4264,13 +4124,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920054</v>
+        <v>21330051920056</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
         <v>136</v>
@@ -4281,13 +4141,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920055</v>
+        <v>21330051920057</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
         <v>137</v>
@@ -4298,13 +4158,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920056</v>
+        <v>21330051920058</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
         <v>138</v>
@@ -4315,13 +4175,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920057</v>
+        <v>21330051920059</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s">
         <v>139</v>
@@ -4332,13 +4192,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920059</v>
+        <v>21330051920060</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s">
         <v>140</v>
@@ -4349,13 +4209,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920060</v>
+        <v>21330051920062</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="D29" t="s">
         <v>141</v>
@@ -4366,13 +4226,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920062</v>
+        <v>21330051920063</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="D30" t="s">
         <v>142</v>
@@ -4383,13 +4243,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920063</v>
+        <v>21330051920065</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="D31" t="s">
         <v>143</v>
@@ -4400,13 +4260,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920065</v>
+        <v>21330051920067</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
         <v>144</v>
@@ -4417,13 +4277,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920067</v>
+        <v>21330051920070</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D33" t="s">
         <v>145</v>
@@ -4439,7 +4299,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4474,13 +4334,13 @@
         <v>21330051920036</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4489,7 +4349,7 @@
         <v>53</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4497,13 +4357,13 @@
         <v>21330051920036</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4520,13 +4380,13 @@
         <v>21330051920037</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4535,7 +4395,7 @@
         <v>53</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4543,13 +4403,13 @@
         <v>21330051920037</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4566,13 +4426,13 @@
         <v>21330051920041</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4581,29 +4441,6 @@
         <v>56</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920046</v>
-      </c>
-      <c r="B7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" t="s">
-        <v>131</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ARHV - Estadisticos 20221.xlsx
+++ b/grupos/3ARHV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -968,7 +968,7 @@
         <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -1004,7 +1004,7 @@
         <v>6</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1045,7 +1045,7 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -1081,7 +1081,7 @@
         <v>9</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>9</v>
@@ -1122,7 +1122,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -1199,7 +1199,7 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -1235,7 +1235,7 @@
         <v>5</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -1276,7 +1276,7 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>6</v>
@@ -1312,7 +1312,7 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>7</v>
@@ -1353,7 +1353,7 @@
         <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>8</v>
@@ -1389,7 +1389,7 @@
         <v>5</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -1507,7 +1507,7 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
         <v>10</v>
@@ -1543,7 +1543,7 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1584,7 +1584,7 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -1661,7 +1661,7 @@
         <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>9</v>
@@ -1738,7 +1738,7 @@
         <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>8</v>
@@ -1774,7 +1774,7 @@
         <v>9</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>9</v>
@@ -1815,7 +1815,7 @@
         <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
         <v>10</v>
@@ -1851,7 +1851,7 @@
         <v>10</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -1892,7 +1892,7 @@
         <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>10</v>
@@ -1969,7 +1969,7 @@
         <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>8</v>
@@ -2005,7 +2005,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2046,7 +2046,7 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>10</v>
@@ -2200,7 +2200,7 @@
         <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
         <v>10</v>
@@ -2277,7 +2277,7 @@
         <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -2313,7 +2313,7 @@
         <v>10</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -2431,7 +2431,7 @@
         <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>8</v>
@@ -2467,7 +2467,7 @@
         <v>9</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>9</v>
@@ -2508,7 +2508,7 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>10</v>
@@ -2585,7 +2585,7 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -2739,7 +2739,7 @@
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>10</v>
@@ -2775,7 +2775,7 @@
         <v>8</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -2816,7 +2816,7 @@
         <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
         <v>10</v>
@@ -2852,7 +2852,7 @@
         <v>8</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -2893,7 +2893,7 @@
         <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
         <v>10</v>
@@ -2970,7 +2970,7 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
         <v>7</v>
@@ -3047,7 +3047,7 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
         <v>8</v>
@@ -3083,7 +3083,7 @@
         <v>8</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -3201,7 +3201,7 @@
         <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>8</v>
@@ -3278,7 +3278,7 @@
         <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>10</v>
@@ -3314,7 +3314,7 @@
         <v>7</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -3549,10 +3549,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C5">
         <v>32</v>
@@ -3561,54 +3561,54 @@
         <v>29</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>90.63</v>
       </c>
       <c r="G5">
-        <v>3.13</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C6">
         <v>32</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>90.63</v>
+        <v>93.75</v>
       </c>
       <c r="G6">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4299,7 +4299,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4421,29 +4421,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920041</v>
-      </c>
-      <c r="B6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>56</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/3ARHV - Estadisticos 20221.xlsx
+++ b/grupos/3ARHV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -962,7 +962,7 @@
         <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -974,7 +974,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -998,7 +998,7 @@
         <v>8</v>
       </c>
       <c r="U4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V4">
         <v>6</v>
@@ -1039,7 +1039,7 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -1051,7 +1051,7 @@
         <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1087,7 +1087,7 @@
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1116,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>10</v>
@@ -1128,7 +1128,7 @@
         <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1164,7 +1164,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1193,7 +1193,7 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -1205,7 +1205,7 @@
         <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1229,7 +1229,7 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1241,7 +1241,7 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1270,7 +1270,7 @@
         <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>9</v>
@@ -1282,7 +1282,7 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1306,7 +1306,7 @@
         <v>8</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1347,7 +1347,7 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>5</v>
@@ -1359,7 +1359,7 @@
         <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1383,7 +1383,7 @@
         <v>9</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>5</v>
@@ -1424,7 +1424,7 @@
         <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -1436,7 +1436,7 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1460,7 +1460,7 @@
         <v>6</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -1501,7 +1501,7 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
         <v>10</v>
@@ -1513,7 +1513,7 @@
         <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1549,7 +1549,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1578,7 +1578,7 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
         <v>10</v>
@@ -1590,7 +1590,7 @@
         <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1614,7 +1614,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1655,7 +1655,7 @@
         <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>9</v>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1703,7 +1703,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1732,7 +1732,7 @@
         <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>9</v>
@@ -1744,7 +1744,7 @@
         <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1768,7 +1768,7 @@
         <v>9</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V14">
         <v>9</v>
@@ -1809,7 +1809,7 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
         <v>10</v>
@@ -1821,7 +1821,7 @@
         <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1857,7 +1857,7 @@
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1886,7 +1886,7 @@
         <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>5</v>
@@ -1898,7 +1898,7 @@
         <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1922,7 +1922,7 @@
         <v>9</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1963,7 +1963,7 @@
         <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
         <v>6</v>
@@ -1975,7 +1975,7 @@
         <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1999,7 +1999,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>7</v>
@@ -2040,7 +2040,7 @@
         <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>10</v>
@@ -2052,7 +2052,7 @@
         <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2076,7 +2076,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>10</v>
@@ -2117,7 +2117,7 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
         <v>7</v>
@@ -2129,7 +2129,7 @@
         <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2194,7 +2194,7 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
         <v>10</v>
@@ -2206,7 +2206,7 @@
         <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2242,7 +2242,7 @@
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2271,7 +2271,7 @@
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
         <v>10</v>
@@ -2283,7 +2283,7 @@
         <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2348,7 +2348,7 @@
         <v>7</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
         <v>5</v>
@@ -2360,7 +2360,7 @@
         <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2425,7 +2425,7 @@
         <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
         <v>9</v>
@@ -2437,7 +2437,7 @@
         <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2461,7 +2461,7 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>9</v>
@@ -2473,7 +2473,7 @@
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2502,7 +2502,7 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
         <v>10</v>
@@ -2514,7 +2514,7 @@
         <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2550,7 +2550,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2579,7 +2579,7 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
         <v>10</v>
@@ -2591,7 +2591,7 @@
         <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2656,7 +2656,7 @@
         <v>7</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>5</v>
@@ -2668,7 +2668,7 @@
         <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2692,7 +2692,7 @@
         <v>6</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>5</v>
@@ -2733,7 +2733,7 @@
         <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
         <v>9</v>
@@ -2745,7 +2745,7 @@
         <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2810,7 +2810,7 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>9</v>
@@ -2822,7 +2822,7 @@
         <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2846,7 +2846,7 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>8</v>
@@ -2858,7 +2858,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2887,7 +2887,7 @@
         <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
         <v>9</v>
@@ -2899,7 +2899,7 @@
         <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2923,7 +2923,7 @@
         <v>10</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -2935,7 +2935,7 @@
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2964,7 +2964,7 @@
         <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
         <v>8</v>
@@ -2976,7 +2976,7 @@
         <v>7</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3041,7 +3041,7 @@
         <v>8</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J31">
         <v>10</v>
@@ -3053,7 +3053,7 @@
         <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3089,7 +3089,7 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3118,7 +3118,7 @@
         <v>5</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>5</v>
@@ -3130,7 +3130,7 @@
         <v>5</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3195,7 +3195,7 @@
         <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
         <v>10</v>
@@ -3207,7 +3207,7 @@
         <v>8</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3272,7 +3272,7 @@
         <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>7</v>
@@ -3284,7 +3284,7 @@
         <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3308,7 +3308,7 @@
         <v>9</v>
       </c>
       <c r="U34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -3349,7 +3349,7 @@
         <v>7</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J35">
         <v>6</v>
@@ -3361,7 +3361,7 @@
         <v>5</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3397,7 +3397,7 @@
         <v>5</v>
       </c>
       <c r="Y35">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3494,19 +3494,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>78.13</v>
+        <v>84.38</v>
       </c>
       <c r="G3">
-        <v>21.88</v>
+        <v>15.63</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3570,7 +3570,7 @@
         <v>9.380000000000001</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4299,7 +4299,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4331,16 +4331,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920036</v>
+        <v>20330051920117</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4354,22 +4354,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920036</v>
+        <v>20330051920117</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4377,16 +4377,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920037</v>
+        <v>21330051920036</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4400,16 +4400,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920037</v>
+        <v>21330051920036</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4418,6 +4418,52 @@
         <v>54</v>
       </c>
       <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920037</v>
+      </c>
+      <c r="B6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920037</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ARHV - Estadisticos 20221.xlsx
+++ b/grupos/3ARHV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -206,247 +206,247 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>OREA</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>TLAXCALTECATL</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>ZETINA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>LEPE</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>XOCHITL JOSELINE</t>
+  </si>
+  <si>
+    <t>GABRIELA ELIZABET</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>ZENON AXXEL</t>
+  </si>
+  <si>
+    <t>GIOVANI</t>
+  </si>
+  <si>
+    <t>EMMANUEL DAVID</t>
+  </si>
+  <si>
+    <t>ZURY BETZABE</t>
+  </si>
+  <si>
+    <t>MIA ARANZA</t>
+  </si>
+  <si>
+    <t>NUBIA NAHOMI</t>
+  </si>
+  <si>
+    <t>MICHEL</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
   </si>
   <si>
     <t>JOSE MANUEL</t>
   </si>
   <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>ANDREA YONETH</t>
+  </si>
+  <si>
+    <t>INGRID CRISTEL</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>SARAHI</t>
+  </si>
+  <si>
+    <t>KARLA JAZMIN</t>
+  </si>
+  <si>
+    <t>YAZURI</t>
+  </si>
+  <si>
     <t>ANIELKA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>TLAXCALTECATL</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>ZETINA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>LEPE</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>XOCHITL JOSELINE</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABET</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
-    <t>ZENON AXXEL</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
-  </si>
-  <si>
-    <t>EMMANUEL DAVID</t>
-  </si>
-  <si>
-    <t>ZURY BETZABE</t>
-  </si>
-  <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>NUBIA NAHOMI</t>
-  </si>
-  <si>
-    <t>MICHEL</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>ANDREA YONETH</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
-  </si>
-  <si>
-    <t>KARLA JAZMIN</t>
-  </si>
-  <si>
-    <t>YAZURI</t>
   </si>
   <si>
     <t>XIMENA</t>
@@ -1430,7 +1430,7 @@
         <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>6</v>
@@ -2123,7 +2123,7 @@
         <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
         <v>8</v>
@@ -2159,7 +2159,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -2336,7 +2336,7 @@
         <v>5</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F22">
         <v>5</v>
@@ -2354,7 +2354,7 @@
         <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>5</v>
@@ -2390,7 +2390,7 @@
         <v>5</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>5</v>
@@ -2662,7 +2662,7 @@
         <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>5</v>
@@ -3106,7 +3106,7 @@
         <v>5</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F32">
         <v>5</v>
@@ -3124,7 +3124,7 @@
         <v>5</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
         <v>5</v>
@@ -3160,7 +3160,7 @@
         <v>5</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X32">
         <v>5</v>
@@ -3355,7 +3355,7 @@
         <v>6</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
         <v>5</v>
@@ -3593,22 +3593,22 @@
         <v>30</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6">
         <v>93.75</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3650,7 +3650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3675,46 +3675,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920053</v>
-      </c>
-      <c r="B2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920064</v>
-      </c>
-      <c r="B3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -3750,47 +3710,47 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920053</v>
+        <v>21330051920029</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920064</v>
+        <v>21330051920031</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920029</v>
+        <v>21330051920034</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
         <v>116</v>
@@ -3801,10 +3761,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920031</v>
+        <v>20330051920117</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
         <v>94</v>
@@ -3818,13 +3778,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920034</v>
+        <v>21330051920035</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
         <v>118</v>
@@ -3835,13 +3795,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920117</v>
+        <v>21330051920036</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
         <v>119</v>
@@ -3852,13 +3812,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920035</v>
+        <v>21330051920037</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
         <v>120</v>
@@ -3869,10 +3829,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920036</v>
+        <v>21330051920038</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
         <v>97</v>
@@ -3886,10 +3846,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920037</v>
+        <v>21330051920390</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
         <v>98</v>
@@ -3903,13 +3863,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920038</v>
+        <v>21330051920040</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
         <v>123</v>
@@ -3920,13 +3880,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920390</v>
+        <v>21330051920041</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
         <v>124</v>
@@ -3937,13 +3897,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920040</v>
+        <v>21330051920043</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
         <v>125</v>
@@ -3954,10 +3914,10 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920041</v>
+        <v>21330051920045</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
         <v>101</v>
@@ -3971,10 +3931,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920043</v>
+        <v>21330051920046</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
         <v>102</v>
@@ -3988,13 +3948,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920045</v>
+        <v>21330051920047</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
         <v>128</v>
@@ -4005,13 +3965,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920046</v>
+        <v>21330051920048</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
         <v>129</v>
@@ -4022,13 +3982,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920047</v>
+        <v>21330051920050</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
         <v>130</v>
@@ -4039,10 +3999,10 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920048</v>
+        <v>21330051920051</v>
       </c>
       <c r="B19" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
         <v>105</v>
@@ -4056,13 +4016,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920050</v>
+        <v>21330051920053</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
         <v>132</v>
@@ -4073,13 +4033,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920051</v>
+        <v>21330051920054</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
@@ -4090,13 +4050,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920054</v>
+        <v>21330051920055</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
         <v>134</v>
@@ -4107,13 +4067,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920055</v>
+        <v>21330051920056</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
         <v>135</v>
@@ -4124,13 +4084,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920056</v>
+        <v>21330051920057</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="D24" t="s">
         <v>136</v>
@@ -4141,13 +4101,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920057</v>
+        <v>21330051920058</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
         <v>137</v>
@@ -4158,13 +4118,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920058</v>
+        <v>21330051920059</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="D26" t="s">
         <v>138</v>
@@ -4175,13 +4135,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920059</v>
+        <v>21330051920060</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s">
         <v>139</v>
@@ -4192,13 +4152,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920060</v>
+        <v>21330051920062</v>
       </c>
       <c r="B28" t="s">
         <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
         <v>140</v>
@@ -4209,13 +4169,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920062</v>
+        <v>21330051920063</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
         <v>141</v>
@@ -4226,13 +4186,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920063</v>
+        <v>21330051920064</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
         <v>142</v>
@@ -4246,10 +4206,10 @@
         <v>21330051920065</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D31" t="s">
         <v>143</v>
@@ -4263,10 +4223,10 @@
         <v>21330051920067</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s">
         <v>144</v>
@@ -4280,10 +4240,10 @@
         <v>21330051920070</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s">
         <v>145</v>
@@ -4334,13 +4294,13 @@
         <v>20330051920117</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4357,13 +4317,13 @@
         <v>20330051920117</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -4380,13 +4340,13 @@
         <v>21330051920036</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4403,13 +4363,13 @@
         <v>21330051920036</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4426,13 +4386,13 @@
         <v>21330051920037</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -4449,13 +4409,13 @@
         <v>21330051920037</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>

--- a/grupos/3ARHV - Estadisticos 20221.xlsx
+++ b/grupos/3ARHV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -989,7 +989,7 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -1007,7 +1007,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -1066,7 +1066,7 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1143,7 +1143,7 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1220,7 +1220,7 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1238,7 +1238,7 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1297,7 +1297,7 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1374,7 +1374,7 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1392,7 +1392,7 @@
         <v>7</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>5</v>
@@ -1451,7 +1451,7 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1469,7 +1469,7 @@
         <v>6</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1528,7 +1528,7 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1605,7 +1605,7 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1623,7 +1623,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1682,7 +1682,7 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1700,7 +1700,7 @@
         <v>9</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1759,7 +1759,7 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1777,7 +1777,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1836,7 +1836,7 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1913,7 +1913,7 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1990,7 +1990,7 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2067,7 +2067,7 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2144,7 +2144,7 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2221,7 +2221,7 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2298,7 +2298,7 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2375,7 +2375,7 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2452,7 +2452,7 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2470,7 +2470,7 @@
         <v>9</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2529,7 +2529,7 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2606,7 +2606,7 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2683,7 +2683,7 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2760,7 +2760,7 @@
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2837,7 +2837,7 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -2914,7 +2914,7 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -2991,7 +2991,7 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3009,7 +3009,7 @@
         <v>9</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>9</v>
@@ -3068,7 +3068,7 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3086,7 +3086,7 @@
         <v>9</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>9</v>
@@ -3145,7 +3145,7 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3222,7 +3222,7 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3240,7 +3240,7 @@
         <v>10</v>
       </c>
       <c r="X33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>9</v>
@@ -3299,7 +3299,7 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3317,7 +3317,7 @@
         <v>7</v>
       </c>
       <c r="X34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y34">
         <v>7</v>
@@ -3376,7 +3376,7 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3526,19 +3526,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="G4">
-        <v>15.63</v>
+        <v>12.5</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4259,7 +4259,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4291,16 +4291,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920117</v>
+        <v>21330051920036</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4314,22 +4314,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920117</v>
+        <v>21330051920036</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4337,16 +4337,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920036</v>
+        <v>21330051920037</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4360,16 +4360,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920036</v>
+        <v>21330051920037</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4383,16 +4383,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920037</v>
+        <v>20330051920117</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -4401,29 +4401,6 @@
         <v>53</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920037</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ARHV - Estadisticos 20221.xlsx
+++ b/grupos/3ARHV - Estadisticos 20221.xlsx
@@ -986,7 +986,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
         <v>7</v>
@@ -1004,7 +1004,7 @@
         <v>6</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>8</v>
@@ -1063,7 +1063,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>10</v>
@@ -1140,7 +1140,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>10</v>
@@ -1217,7 +1217,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
         <v>7</v>
@@ -1235,7 +1235,7 @@
         <v>5</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1294,7 +1294,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
         <v>6</v>
@@ -1312,7 +1312,7 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>7</v>
@@ -1371,7 +1371,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
         <v>10</v>
@@ -1448,7 +1448,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
         <v>5</v>
@@ -1525,7 +1525,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
         <v>10</v>
@@ -1543,7 +1543,7 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1602,7 +1602,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>5</v>
@@ -1620,7 +1620,7 @@
         <v>9</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1679,7 +1679,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>7</v>
@@ -1697,7 +1697,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>8</v>
@@ -1756,7 +1756,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>7</v>
@@ -1774,7 +1774,7 @@
         <v>9</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -1833,7 +1833,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>10</v>
@@ -1910,7 +1910,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
         <v>10</v>
@@ -1987,7 +1987,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>8</v>
@@ -2064,7 +2064,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
         <v>10</v>
@@ -2141,7 +2141,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>8</v>
@@ -2159,7 +2159,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -2218,7 +2218,7 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>10</v>
@@ -2295,7 +2295,7 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
         <v>10</v>
@@ -2313,7 +2313,7 @@
         <v>10</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>5</v>
@@ -2449,7 +2449,7 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>8</v>
@@ -2526,7 +2526,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>10</v>
@@ -2603,7 +2603,7 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>10</v>
@@ -2680,7 +2680,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
         <v>5</v>
@@ -2698,7 +2698,7 @@
         <v>5</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>5</v>
@@ -2757,7 +2757,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
         <v>10</v>
@@ -2775,7 +2775,7 @@
         <v>8</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -2834,7 +2834,7 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
         <v>10</v>
@@ -2911,7 +2911,7 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>10</v>
@@ -2988,7 +2988,7 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>6</v>
@@ -3065,7 +3065,7 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
         <v>6</v>
@@ -3083,7 +3083,7 @@
         <v>8</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -3142,7 +3142,7 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R32">
         <v>5</v>
@@ -3219,7 +3219,7 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
         <v>7</v>
@@ -3237,7 +3237,7 @@
         <v>9</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -3296,7 +3296,7 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R34">
         <v>8</v>
@@ -3602,7 +3602,7 @@
         <v>6.25</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/3ARHV - Estadisticos 20221.xlsx
+++ b/grupos/3ARHV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="146">
   <si>
     <t>Materia</t>
   </si>
@@ -977,13 +977,13 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
         <v>7</v>
@@ -992,7 +992,7 @@
         <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>8</v>
@@ -1054,13 +1054,13 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
         <v>10</v>
@@ -1069,10 +1069,10 @@
         <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>9</v>
@@ -1131,13 +1131,13 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
         <v>10</v>
@@ -1146,13 +1146,13 @@
         <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>10</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -1164,7 +1164,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1208,13 +1208,13 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>7</v>
@@ -1223,16 +1223,16 @@
         <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>7</v>
@@ -1285,13 +1285,13 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
         <v>7</v>
@@ -1300,7 +1300,7 @@
         <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>8</v>
@@ -1309,7 +1309,7 @@
         <v>9</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1318,7 +1318,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1362,13 +1362,13 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>7</v>
@@ -1377,7 +1377,7 @@
         <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>9</v>
@@ -1395,7 +1395,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1439,13 +1439,13 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
         <v>6</v>
@@ -1454,7 +1454,7 @@
         <v>5</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>6</v>
@@ -1472,7 +1472,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1516,13 +1516,13 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
         <v>9</v>
@@ -1531,16 +1531,16 @@
         <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>10</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1549,7 +1549,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1593,13 +1593,13 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>8</v>
@@ -1608,13 +1608,13 @@
         <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1670,13 +1670,13 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>8</v>
@@ -1685,16 +1685,16 @@
         <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1703,7 +1703,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1747,13 +1747,13 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
         <v>9</v>
@@ -1762,7 +1762,7 @@
         <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1771,7 +1771,7 @@
         <v>9</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1780,7 +1780,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1824,13 +1824,13 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
         <v>8</v>
@@ -1839,7 +1839,7 @@
         <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1901,13 +1901,13 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>7</v>
@@ -1916,7 +1916,7 @@
         <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1978,13 +1978,13 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <v>8</v>
@@ -1993,16 +1993,16 @@
         <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>9</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -2011,7 +2011,7 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2055,13 +2055,13 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>9</v>
@@ -2070,7 +2070,7 @@
         <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -2132,13 +2132,13 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
         <v>8</v>
@@ -2147,13 +2147,13 @@
         <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
         <v>7</v>
@@ -2209,13 +2209,13 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
         <v>10</v>
@@ -2224,16 +2224,16 @@
         <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>10</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -2242,7 +2242,7 @@
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2286,13 +2286,13 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
         <v>9</v>
@@ -2301,16 +2301,16 @@
         <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>9</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2319,7 +2319,7 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2363,13 +2363,13 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>5</v>
@@ -2378,10 +2378,10 @@
         <v>5</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>5</v>
@@ -2440,13 +2440,13 @@
         <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
         <v>10</v>
@@ -2455,13 +2455,13 @@
         <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
         <v>10</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>9</v>
@@ -2517,13 +2517,13 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
         <v>10</v>
@@ -2532,7 +2532,7 @@
         <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2594,13 +2594,13 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>10</v>
@@ -2609,7 +2609,7 @@
         <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2618,7 +2618,7 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>10</v>
@@ -2671,13 +2671,13 @@
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
         <v>5</v>
@@ -2686,13 +2686,13 @@
         <v>5</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T26">
         <v>6</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V26">
         <v>5</v>
@@ -2748,13 +2748,13 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
         <v>9</v>
@@ -2763,16 +2763,16 @@
         <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>9</v>
@@ -2781,7 +2781,7 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2825,13 +2825,13 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>8</v>
@@ -2840,16 +2840,16 @@
         <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>8</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2902,13 +2902,13 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>10</v>
@@ -2917,7 +2917,7 @@
         <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -2979,13 +2979,13 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
         <v>9</v>
@@ -2994,13 +2994,13 @@
         <v>6</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>8</v>
@@ -3012,7 +3012,7 @@
         <v>7</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3056,13 +3056,13 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
         <v>7</v>
@@ -3071,7 +3071,7 @@
         <v>6</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -3080,7 +3080,7 @@
         <v>8</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>8</v>
@@ -3089,7 +3089,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3133,13 +3133,13 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
         <v>5</v>
@@ -3148,7 +3148,7 @@
         <v>5</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T32">
         <v>5</v>
@@ -3210,13 +3210,13 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
         <v>8</v>
@@ -3225,10 +3225,10 @@
         <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U33">
         <v>9</v>
@@ -3287,13 +3287,13 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>8</v>
@@ -3302,13 +3302,13 @@
         <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
         <v>9</v>
       </c>
       <c r="U34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -3364,13 +3364,13 @@
         <v>7</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -3379,10 +3379,10 @@
         <v>5</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U35">
         <v>5</v>
@@ -3397,7 +3397,7 @@
         <v>5</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3462,19 +3462,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>78.13</v>
+        <v>81.25</v>
       </c>
       <c r="G2">
-        <v>21.88</v>
+        <v>18.75</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3494,19 +3494,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="G3">
-        <v>15.63</v>
+        <v>12.5</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3517,10 +3517,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>32</v>
@@ -3538,7 +3538,7 @@
         <v>12.5</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3549,28 +3549,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5">
         <v>32</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>90.63</v>
+        <v>87.5</v>
       </c>
       <c r="G5">
-        <v>9.380000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3634,7 +3634,7 @@
         <v>3.13</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4259,7 +4259,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4314,93 +4314,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920036</v>
+        <v>21330051920037</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920037</v>
-      </c>
-      <c r="B4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920037</v>
-      </c>
-      <c r="B5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920117</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ARHV - Estadisticos 20221.xlsx
+++ b/grupos/3ARHV - Estadisticos 20221.xlsx
@@ -3373,7 +3373,7 @@
         <v>5</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R35">
         <v>5</v>
